--- a/artfynd/A 43108-2021 artfynd.xlsx
+++ b/artfynd/A 43108-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 43108-2021 artfynd.xlsx
+++ b/artfynd/A 43108-2021 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>112182922</v>
+        <v>112183919</v>
       </c>
       <c r="B2" t="n">
-        <v>77689</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>541767</v>
+        <v>541671</v>
       </c>
       <c r="R2" t="n">
-        <v>6874916</v>
+        <v>6874837</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -786,37 +781,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>112183123</v>
+        <v>112183492</v>
       </c>
       <c r="B3" t="n">
-        <v>96775</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92369</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -830,10 +820,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>541878</v>
+        <v>541897</v>
       </c>
       <c r="R3" t="n">
-        <v>6874843</v>
+        <v>6874858</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -897,37 +887,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>112183113</v>
+        <v>112182886</v>
       </c>
       <c r="B4" t="n">
-        <v>96775</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>1312</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -941,10 +926,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>541872</v>
+        <v>541897</v>
       </c>
       <c r="R4" t="n">
-        <v>6874869</v>
+        <v>6874858</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1008,15 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>112183117</v>
+        <v>112182920</v>
       </c>
       <c r="B5" t="n">
-        <v>96775</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1024,21 +1004,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1052,10 +1032,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>541710</v>
+        <v>541681</v>
       </c>
       <c r="R5" t="n">
-        <v>6874837</v>
+        <v>6874847</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1119,15 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>112183116</v>
+        <v>112182922</v>
       </c>
       <c r="B6" t="n">
-        <v>96775</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1135,21 +1110,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1163,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>541718</v>
+        <v>541767</v>
       </c>
       <c r="R6" t="n">
-        <v>6874869</v>
+        <v>6874916</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1230,15 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>112183125</v>
+        <v>112182925</v>
       </c>
       <c r="B7" t="n">
-        <v>96775</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1246,21 +1216,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1274,10 +1244,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>541888</v>
+        <v>541897</v>
       </c>
       <c r="R7" t="n">
-        <v>6874834</v>
+        <v>6874857</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1341,37 +1311,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>112183121</v>
+        <v>112183238</v>
       </c>
       <c r="B8" t="n">
-        <v>96775</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1385,10 +1350,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>541839</v>
+        <v>541919</v>
       </c>
       <c r="R8" t="n">
-        <v>6874873</v>
+        <v>6874882</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1452,15 +1417,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>112183919</v>
+        <v>112183239</v>
       </c>
       <c r="B9" t="n">
-        <v>89592</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1468,21 +1428,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1496,10 +1456,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>541671</v>
+        <v>541723</v>
       </c>
       <c r="R9" t="n">
-        <v>6874836</v>
+        <v>6874878</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1566,12 +1526,7 @@
         <v>112183240</v>
       </c>
       <c r="B10" t="n">
-        <v>78752</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1610,7 +1565,7 @@
         <v>541732</v>
       </c>
       <c r="R10" t="n">
-        <v>6874874</v>
+        <v>6874875</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1674,15 +1629,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>112182925</v>
+        <v>112183241</v>
       </c>
       <c r="B11" t="n">
-        <v>77689</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1690,21 +1640,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1718,10 +1668,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>541897</v>
+        <v>541843</v>
       </c>
       <c r="R11" t="n">
-        <v>6874858</v>
+        <v>6874864</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1785,15 +1735,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>112182886</v>
+        <v>112183243</v>
       </c>
       <c r="B12" t="n">
-        <v>81424</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1801,21 +1746,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1312</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1829,10 +1774,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>541897</v>
+        <v>541882</v>
       </c>
       <c r="R12" t="n">
-        <v>6874859</v>
+        <v>6874855</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1896,37 +1841,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>112183239</v>
+        <v>112183111</v>
       </c>
       <c r="B13" t="n">
-        <v>78752</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1940,10 +1880,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>541723</v>
+        <v>541896</v>
       </c>
       <c r="R13" t="n">
-        <v>6874878</v>
+        <v>6874881</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2007,15 +1947,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>112183492</v>
+        <v>112183113</v>
       </c>
       <c r="B14" t="n">
-        <v>90032</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2023,21 +1958,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -2051,10 +1986,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>541897</v>
+        <v>541872</v>
       </c>
       <c r="R14" t="n">
-        <v>6874859</v>
+        <v>6874869</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2118,15 +2053,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>112183132</v>
+        <v>112183116</v>
       </c>
       <c r="B15" t="n">
-        <v>96775</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2162,10 +2092,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>541898</v>
+        <v>541718</v>
       </c>
       <c r="R15" t="n">
-        <v>6874891</v>
+        <v>6874869</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2229,15 +2159,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>112183126</v>
+        <v>112183117</v>
       </c>
       <c r="B16" t="n">
-        <v>96775</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2273,10 +2198,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>541884</v>
+        <v>541710</v>
       </c>
       <c r="R16" t="n">
-        <v>6874841</v>
+        <v>6874837</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2340,37 +2265,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>112182920</v>
+        <v>112183119</v>
       </c>
       <c r="B17" t="n">
-        <v>77689</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2384,10 +2304,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>541681</v>
+        <v>541832</v>
       </c>
       <c r="R17" t="n">
-        <v>6874847</v>
+        <v>6874903</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2451,15 +2371,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>112183130</v>
+        <v>112183121</v>
       </c>
       <c r="B18" t="n">
-        <v>96775</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2495,10 +2410,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>541895</v>
+        <v>541839</v>
       </c>
       <c r="R18" t="n">
-        <v>6874883</v>
+        <v>6874873</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2562,37 +2477,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>112183241</v>
+        <v>112183123</v>
       </c>
       <c r="B19" t="n">
-        <v>78752</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2606,10 +2516,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>541843</v>
+        <v>541878</v>
       </c>
       <c r="R19" t="n">
-        <v>6874864</v>
+        <v>6874843</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2673,37 +2583,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>112183238</v>
+        <v>112183125</v>
       </c>
       <c r="B20" t="n">
-        <v>78752</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2717,10 +2622,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>541920</v>
+        <v>541888</v>
       </c>
       <c r="R20" t="n">
-        <v>6874882</v>
+        <v>6874834</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2784,37 +2689,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>112183243</v>
+        <v>112183126</v>
       </c>
       <c r="B21" t="n">
-        <v>78752</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2828,10 +2728,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>541882</v>
+        <v>541884</v>
       </c>
       <c r="R21" t="n">
-        <v>6874855</v>
+        <v>6874841</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2898,12 +2798,7 @@
         <v>112183128</v>
       </c>
       <c r="B22" t="n">
-        <v>96775</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2939,10 +2834,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>541889</v>
+        <v>541888</v>
       </c>
       <c r="R22" t="n">
-        <v>6874872</v>
+        <v>6874871</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3006,15 +2901,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>112183119</v>
+        <v>112183130</v>
       </c>
       <c r="B23" t="n">
-        <v>96775</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3050,10 +2940,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>541832</v>
+        <v>541894</v>
       </c>
       <c r="R23" t="n">
-        <v>6874903</v>
+        <v>6874884</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3117,15 +3007,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>112183111</v>
+        <v>112183132</v>
       </c>
       <c r="B24" t="n">
-        <v>96775</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3161,10 +3046,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>541897</v>
+        <v>541899</v>
       </c>
       <c r="R24" t="n">
-        <v>6874882</v>
+        <v>6874892</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>

--- a/artfynd/A 43108-2021 artfynd.xlsx
+++ b/artfynd/A 43108-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY24"/>
+  <dimension ref="A1:AZ24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -778,6 +783,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112183919</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -884,6 +894,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112183492</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -990,6 +1005,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112182886</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1096,6 +1116,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112182920</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1202,6 +1227,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112182922</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1308,6 +1338,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112182925</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1414,6 +1449,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112183238</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1520,6 +1560,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112183239</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1626,6 +1671,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112183240</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1732,6 +1782,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112183241</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1838,6 +1893,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112183243</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1944,6 +2004,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112183111</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2050,6 +2115,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112183113</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2156,6 +2226,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112183116</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2262,6 +2337,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112183117</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2368,6 +2448,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112183119</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2474,6 +2559,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112183121</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2580,6 +2670,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112183123</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2686,6 +2781,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112183125</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2792,6 +2892,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112183126</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2898,6 +3003,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112183128</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3004,6 +3114,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112183130</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3110,8 +3225,38 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112183132</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>